--- a/BD_Requerimientos_POs.xlsx
+++ b/BD_Requerimientos_POs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E422"/>
+  <dimension ref="A1:E439"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10968,6 +10968,431 @@
         </is>
       </c>
     </row>
+    <row r="423">
+      <c r="A423" t="inlineStr">
+        <is>
+          <t>26030989</t>
+        </is>
+      </c>
+      <c r="B423" t="inlineStr">
+        <is>
+          <t>12-C-6210-02</t>
+        </is>
+      </c>
+      <c r="C423" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="D423" t="n">
+        <v>128</v>
+      </c>
+      <c r="E423" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" t="inlineStr">
+        <is>
+          <t>26030989</t>
+        </is>
+      </c>
+      <c r="B424" t="inlineStr">
+        <is>
+          <t>11-A-6014-01</t>
+        </is>
+      </c>
+      <c r="C424" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="D424" t="n">
+        <v>240</v>
+      </c>
+      <c r="E424" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" t="inlineStr">
+        <is>
+          <t>26030989</t>
+        </is>
+      </c>
+      <c r="B425" t="inlineStr">
+        <is>
+          <t>12-D-6091-06</t>
+        </is>
+      </c>
+      <c r="C425" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="D425" t="n">
+        <v>4</v>
+      </c>
+      <c r="E425" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" t="inlineStr">
+        <is>
+          <t>26030989</t>
+        </is>
+      </c>
+      <c r="B426" t="inlineStr">
+        <is>
+          <t>11-A-6004-01</t>
+        </is>
+      </c>
+      <c r="C426" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="D426" t="n">
+        <v>136</v>
+      </c>
+      <c r="E426" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" t="inlineStr">
+        <is>
+          <t>26030989</t>
+        </is>
+      </c>
+      <c r="B427" t="inlineStr">
+        <is>
+          <t>12-6010-03</t>
+        </is>
+      </c>
+      <c r="C427" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="D427" t="n">
+        <v>16</v>
+      </c>
+      <c r="E427" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" t="inlineStr">
+        <is>
+          <t>26030989</t>
+        </is>
+      </c>
+      <c r="B428" t="inlineStr">
+        <is>
+          <t>12-D-6033-05</t>
+        </is>
+      </c>
+      <c r="C428" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="D428" t="n">
+        <v>136</v>
+      </c>
+      <c r="E428" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" t="inlineStr">
+        <is>
+          <t>26030989</t>
+        </is>
+      </c>
+      <c r="B429" t="inlineStr">
+        <is>
+          <t>12-6010-01</t>
+        </is>
+      </c>
+      <c r="C429" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="D429" t="n">
+        <v>48</v>
+      </c>
+      <c r="E429" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" t="inlineStr">
+        <is>
+          <t>26030989</t>
+        </is>
+      </c>
+      <c r="B430" t="inlineStr">
+        <is>
+          <t>PP21341-12</t>
+        </is>
+      </c>
+      <c r="C430" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="D430" t="n">
+        <v>60</v>
+      </c>
+      <c r="E430" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" t="inlineStr">
+        <is>
+          <t>26030989</t>
+        </is>
+      </c>
+      <c r="B431" t="inlineStr">
+        <is>
+          <t>12-6010-02</t>
+        </is>
+      </c>
+      <c r="C431" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="D431" t="n">
+        <v>12</v>
+      </c>
+      <c r="E431" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" t="inlineStr">
+        <is>
+          <t>26030989</t>
+        </is>
+      </c>
+      <c r="B432" t="inlineStr">
+        <is>
+          <t>12-6010-05</t>
+        </is>
+      </c>
+      <c r="C432" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="D432" t="n">
+        <v>4</v>
+      </c>
+      <c r="E432" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" t="inlineStr">
+        <is>
+          <t>26030989</t>
+        </is>
+      </c>
+      <c r="B433" t="inlineStr">
+        <is>
+          <t>12-6010-10</t>
+        </is>
+      </c>
+      <c r="C433" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="D433" t="n">
+        <v>104</v>
+      </c>
+      <c r="E433" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" t="inlineStr">
+        <is>
+          <t>26030989</t>
+        </is>
+      </c>
+      <c r="B434" t="inlineStr">
+        <is>
+          <t>12-C-6210-01</t>
+        </is>
+      </c>
+      <c r="C434" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="D434" t="n">
+        <v>8</v>
+      </c>
+      <c r="E434" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" t="inlineStr">
+        <is>
+          <t>26030989</t>
+        </is>
+      </c>
+      <c r="B435" t="inlineStr">
+        <is>
+          <t>PP15536-02</t>
+        </is>
+      </c>
+      <c r="C435" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="D435" t="n">
+        <v>8</v>
+      </c>
+      <c r="E435" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" t="inlineStr">
+        <is>
+          <t>26030989</t>
+        </is>
+      </c>
+      <c r="B436" t="inlineStr">
+        <is>
+          <t>PP21340-02</t>
+        </is>
+      </c>
+      <c r="C436" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="D436" t="n">
+        <v>56</v>
+      </c>
+      <c r="E436" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" t="inlineStr">
+        <is>
+          <t>26030989</t>
+        </is>
+      </c>
+      <c r="B437" t="inlineStr">
+        <is>
+          <t>PP21340-03</t>
+        </is>
+      </c>
+      <c r="C437" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="D437" t="n">
+        <v>4</v>
+      </c>
+      <c r="E437" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" t="inlineStr">
+        <is>
+          <t>26030989</t>
+        </is>
+      </c>
+      <c r="B438" t="inlineStr">
+        <is>
+          <t>PP7517-10</t>
+        </is>
+      </c>
+      <c r="C438" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="D438" t="n">
+        <v>320</v>
+      </c>
+      <c r="E438" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" t="inlineStr">
+        <is>
+          <t>26030989</t>
+        </is>
+      </c>
+      <c r="B439" t="inlineStr">
+        <is>
+          <t>P20365-02</t>
+        </is>
+      </c>
+      <c r="C439" t="inlineStr">
+        <is>
+          <t>2026-03-31</t>
+        </is>
+      </c>
+      <c r="D439" t="n">
+        <v>8</v>
+      </c>
+      <c r="E439" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BD_Requerimientos_POs.xlsx
+++ b/BD_Requerimientos_POs.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E439"/>
+  <dimension ref="A1:E422"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10968,431 +10968,6 @@
         </is>
       </c>
     </row>
-    <row r="423">
-      <c r="A423" t="inlineStr">
-        <is>
-          <t>26030989</t>
-        </is>
-      </c>
-      <c r="B423" t="inlineStr">
-        <is>
-          <t>12-C-6210-02</t>
-        </is>
-      </c>
-      <c r="C423" t="inlineStr">
-        <is>
-          <t>2026-03-31</t>
-        </is>
-      </c>
-      <c r="D423" t="n">
-        <v>128</v>
-      </c>
-      <c r="E423" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-    </row>
-    <row r="424">
-      <c r="A424" t="inlineStr">
-        <is>
-          <t>26030989</t>
-        </is>
-      </c>
-      <c r="B424" t="inlineStr">
-        <is>
-          <t>11-A-6014-01</t>
-        </is>
-      </c>
-      <c r="C424" t="inlineStr">
-        <is>
-          <t>2026-03-31</t>
-        </is>
-      </c>
-      <c r="D424" t="n">
-        <v>240</v>
-      </c>
-      <c r="E424" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-    </row>
-    <row r="425">
-      <c r="A425" t="inlineStr">
-        <is>
-          <t>26030989</t>
-        </is>
-      </c>
-      <c r="B425" t="inlineStr">
-        <is>
-          <t>12-D-6091-06</t>
-        </is>
-      </c>
-      <c r="C425" t="inlineStr">
-        <is>
-          <t>2026-03-31</t>
-        </is>
-      </c>
-      <c r="D425" t="n">
-        <v>4</v>
-      </c>
-      <c r="E425" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-    </row>
-    <row r="426">
-      <c r="A426" t="inlineStr">
-        <is>
-          <t>26030989</t>
-        </is>
-      </c>
-      <c r="B426" t="inlineStr">
-        <is>
-          <t>11-A-6004-01</t>
-        </is>
-      </c>
-      <c r="C426" t="inlineStr">
-        <is>
-          <t>2026-03-31</t>
-        </is>
-      </c>
-      <c r="D426" t="n">
-        <v>136</v>
-      </c>
-      <c r="E426" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-    </row>
-    <row r="427">
-      <c r="A427" t="inlineStr">
-        <is>
-          <t>26030989</t>
-        </is>
-      </c>
-      <c r="B427" t="inlineStr">
-        <is>
-          <t>12-6010-03</t>
-        </is>
-      </c>
-      <c r="C427" t="inlineStr">
-        <is>
-          <t>2026-03-31</t>
-        </is>
-      </c>
-      <c r="D427" t="n">
-        <v>16</v>
-      </c>
-      <c r="E427" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-    </row>
-    <row r="428">
-      <c r="A428" t="inlineStr">
-        <is>
-          <t>26030989</t>
-        </is>
-      </c>
-      <c r="B428" t="inlineStr">
-        <is>
-          <t>12-D-6033-05</t>
-        </is>
-      </c>
-      <c r="C428" t="inlineStr">
-        <is>
-          <t>2026-03-31</t>
-        </is>
-      </c>
-      <c r="D428" t="n">
-        <v>136</v>
-      </c>
-      <c r="E428" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-    </row>
-    <row r="429">
-      <c r="A429" t="inlineStr">
-        <is>
-          <t>26030989</t>
-        </is>
-      </c>
-      <c r="B429" t="inlineStr">
-        <is>
-          <t>12-6010-01</t>
-        </is>
-      </c>
-      <c r="C429" t="inlineStr">
-        <is>
-          <t>2026-03-31</t>
-        </is>
-      </c>
-      <c r="D429" t="n">
-        <v>48</v>
-      </c>
-      <c r="E429" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-    </row>
-    <row r="430">
-      <c r="A430" t="inlineStr">
-        <is>
-          <t>26030989</t>
-        </is>
-      </c>
-      <c r="B430" t="inlineStr">
-        <is>
-          <t>PP21341-12</t>
-        </is>
-      </c>
-      <c r="C430" t="inlineStr">
-        <is>
-          <t>2026-03-31</t>
-        </is>
-      </c>
-      <c r="D430" t="n">
-        <v>60</v>
-      </c>
-      <c r="E430" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-    </row>
-    <row r="431">
-      <c r="A431" t="inlineStr">
-        <is>
-          <t>26030989</t>
-        </is>
-      </c>
-      <c r="B431" t="inlineStr">
-        <is>
-          <t>12-6010-02</t>
-        </is>
-      </c>
-      <c r="C431" t="inlineStr">
-        <is>
-          <t>2026-03-31</t>
-        </is>
-      </c>
-      <c r="D431" t="n">
-        <v>12</v>
-      </c>
-      <c r="E431" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-    </row>
-    <row r="432">
-      <c r="A432" t="inlineStr">
-        <is>
-          <t>26030989</t>
-        </is>
-      </c>
-      <c r="B432" t="inlineStr">
-        <is>
-          <t>12-6010-05</t>
-        </is>
-      </c>
-      <c r="C432" t="inlineStr">
-        <is>
-          <t>2026-03-31</t>
-        </is>
-      </c>
-      <c r="D432" t="n">
-        <v>4</v>
-      </c>
-      <c r="E432" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-    </row>
-    <row r="433">
-      <c r="A433" t="inlineStr">
-        <is>
-          <t>26030989</t>
-        </is>
-      </c>
-      <c r="B433" t="inlineStr">
-        <is>
-          <t>12-6010-10</t>
-        </is>
-      </c>
-      <c r="C433" t="inlineStr">
-        <is>
-          <t>2026-03-31</t>
-        </is>
-      </c>
-      <c r="D433" t="n">
-        <v>104</v>
-      </c>
-      <c r="E433" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-    </row>
-    <row r="434">
-      <c r="A434" t="inlineStr">
-        <is>
-          <t>26030989</t>
-        </is>
-      </c>
-      <c r="B434" t="inlineStr">
-        <is>
-          <t>12-C-6210-01</t>
-        </is>
-      </c>
-      <c r="C434" t="inlineStr">
-        <is>
-          <t>2026-03-31</t>
-        </is>
-      </c>
-      <c r="D434" t="n">
-        <v>8</v>
-      </c>
-      <c r="E434" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-    </row>
-    <row r="435">
-      <c r="A435" t="inlineStr">
-        <is>
-          <t>26030989</t>
-        </is>
-      </c>
-      <c r="B435" t="inlineStr">
-        <is>
-          <t>PP15536-02</t>
-        </is>
-      </c>
-      <c r="C435" t="inlineStr">
-        <is>
-          <t>2026-03-31</t>
-        </is>
-      </c>
-      <c r="D435" t="n">
-        <v>8</v>
-      </c>
-      <c r="E435" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-    </row>
-    <row r="436">
-      <c r="A436" t="inlineStr">
-        <is>
-          <t>26030989</t>
-        </is>
-      </c>
-      <c r="B436" t="inlineStr">
-        <is>
-          <t>PP21340-02</t>
-        </is>
-      </c>
-      <c r="C436" t="inlineStr">
-        <is>
-          <t>2026-03-31</t>
-        </is>
-      </c>
-      <c r="D436" t="n">
-        <v>56</v>
-      </c>
-      <c r="E436" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-    </row>
-    <row r="437">
-      <c r="A437" t="inlineStr">
-        <is>
-          <t>26030989</t>
-        </is>
-      </c>
-      <c r="B437" t="inlineStr">
-        <is>
-          <t>PP21340-03</t>
-        </is>
-      </c>
-      <c r="C437" t="inlineStr">
-        <is>
-          <t>2026-03-31</t>
-        </is>
-      </c>
-      <c r="D437" t="n">
-        <v>4</v>
-      </c>
-      <c r="E437" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-    </row>
-    <row r="438">
-      <c r="A438" t="inlineStr">
-        <is>
-          <t>26030989</t>
-        </is>
-      </c>
-      <c r="B438" t="inlineStr">
-        <is>
-          <t>PP7517-10</t>
-        </is>
-      </c>
-      <c r="C438" t="inlineStr">
-        <is>
-          <t>2026-03-31</t>
-        </is>
-      </c>
-      <c r="D438" t="n">
-        <v>320</v>
-      </c>
-      <c r="E438" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-    </row>
-    <row r="439">
-      <c r="A439" t="inlineStr">
-        <is>
-          <t>26030989</t>
-        </is>
-      </c>
-      <c r="B439" t="inlineStr">
-        <is>
-          <t>P20365-02</t>
-        </is>
-      </c>
-      <c r="C439" t="inlineStr">
-        <is>
-          <t>2026-03-31</t>
-        </is>
-      </c>
-      <c r="D439" t="n">
-        <v>8</v>
-      </c>
-      <c r="E439" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BD_Requerimientos_POs.xlsx
+++ b/BD_Requerimientos_POs.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Datos_Sistema" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Datos_Sistema" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -446,7 +446,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -471,7 +471,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -496,7 +496,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -521,7 +521,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -546,7 +546,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -571,7 +571,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -596,7 +596,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -621,7 +621,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -646,7 +646,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -671,7 +671,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -696,7 +696,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -721,7 +721,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -746,7 +746,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -771,7 +771,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -796,7 +796,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -821,7 +821,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -846,7 +846,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -871,7 +871,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -896,7 +896,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -921,7 +921,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -946,7 +946,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -971,7 +971,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -996,7 +996,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1021,7 +1021,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1046,7 +1046,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1071,7 +1071,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1096,7 +1096,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1121,7 +1121,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1146,7 +1146,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1171,7 +1171,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1196,7 +1196,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1221,7 +1221,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1246,7 +1246,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1271,7 +1271,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1296,7 +1296,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1321,7 +1321,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1346,7 +1346,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1371,7 +1371,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1396,7 +1396,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1421,7 +1421,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1446,7 +1446,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1471,7 +1471,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1496,7 +1496,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1521,7 +1521,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1546,7 +1546,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1571,7 +1571,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -1596,7 +1596,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -1621,7 +1621,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -1646,7 +1646,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -1671,7 +1671,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -1696,7 +1696,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -1721,7 +1721,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -1746,7 +1746,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -1771,7 +1771,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -1796,7 +1796,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -1821,7 +1821,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -1846,7 +1846,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -1871,7 +1871,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -1896,7 +1896,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -1921,7 +1921,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -1946,7 +1946,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -1971,7 +1971,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -1996,7 +1996,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2021,7 +2021,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2046,7 +2046,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2071,7 +2071,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2096,7 +2096,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2121,7 +2121,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2146,7 +2146,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2171,7 +2171,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -2196,7 +2196,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -2221,7 +2221,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -2246,7 +2246,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -2271,7 +2271,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -2296,7 +2296,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -2321,7 +2321,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -2346,7 +2346,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -2371,7 +2371,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -2396,7 +2396,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -2421,7 +2421,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -2446,7 +2446,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -2471,7 +2471,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -2496,7 +2496,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -2521,7 +2521,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -2546,7 +2546,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -2571,7 +2571,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -2596,7 +2596,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -2621,7 +2621,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -2646,7 +2646,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -2671,7 +2671,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -2696,7 +2696,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -2721,7 +2721,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -2746,7 +2746,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -2771,7 +2771,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -2796,7 +2796,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -2821,7 +2821,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -2846,7 +2846,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -2871,7 +2871,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -2896,7 +2896,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -2921,7 +2921,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -2946,7 +2946,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -2971,7 +2971,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -2996,7 +2996,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -3021,7 +3021,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -3046,7 +3046,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -3071,7 +3071,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -3096,7 +3096,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -3121,7 +3121,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -3146,7 +3146,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -3171,7 +3171,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -3196,7 +3196,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -3221,7 +3221,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -3246,7 +3246,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -3271,7 +3271,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -3296,7 +3296,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -3321,7 +3321,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -3346,7 +3346,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -3371,7 +3371,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -3396,7 +3396,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -3421,7 +3421,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -3446,7 +3446,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -3471,7 +3471,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -3496,7 +3496,7 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -3521,7 +3521,7 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -3546,7 +3546,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -3571,7 +3571,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -3596,7 +3596,7 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -3621,7 +3621,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -3646,7 +3646,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -3671,7 +3671,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -3696,7 +3696,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -3721,7 +3721,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -3746,7 +3746,7 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -3771,7 +3771,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -3796,7 +3796,7 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -3821,7 +3821,7 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -3846,7 +3846,7 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -3871,7 +3871,7 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -3896,7 +3896,7 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -3921,7 +3921,7 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -3946,7 +3946,7 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -3971,7 +3971,7 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -3996,7 +3996,7 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -4021,7 +4021,7 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -4046,7 +4046,7 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -4071,7 +4071,7 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -4096,7 +4096,7 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -4121,7 +4121,7 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -4146,7 +4146,7 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -4171,7 +4171,7 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -4196,7 +4196,7 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -4221,7 +4221,7 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -4246,7 +4246,7 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -4271,7 +4271,7 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -4296,7 +4296,7 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -4321,7 +4321,7 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -4346,7 +4346,7 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -4371,7 +4371,7 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -4396,7 +4396,7 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -4421,7 +4421,7 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -4446,7 +4446,7 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -4471,7 +4471,7 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -4496,7 +4496,7 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -4521,7 +4521,7 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -4546,7 +4546,7 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -4571,7 +4571,7 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -4596,7 +4596,7 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -4621,7 +4621,7 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -4646,7 +4646,7 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -4671,7 +4671,7 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -4696,7 +4696,7 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -4721,7 +4721,7 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -4746,7 +4746,7 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -4771,7 +4771,7 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -4796,7 +4796,7 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -4821,7 +4821,7 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -4846,7 +4846,7 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -4871,7 +4871,7 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -4896,7 +4896,7 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -4921,7 +4921,7 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -4946,7 +4946,7 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -4971,7 +4971,7 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -4996,7 +4996,7 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -5021,7 +5021,7 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -5046,7 +5046,7 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -5071,7 +5071,7 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -5096,7 +5096,7 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -5121,7 +5121,7 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -5146,7 +5146,7 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -5171,7 +5171,7 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -5196,7 +5196,7 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -5221,7 +5221,7 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -5246,7 +5246,7 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -5271,7 +5271,7 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -5296,7 +5296,7 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -5321,7 +5321,7 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -5346,7 +5346,7 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -5371,7 +5371,7 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -5396,7 +5396,7 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -5421,7 +5421,7 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -5446,7 +5446,7 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -5471,7 +5471,7 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -5496,7 +5496,7 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -5521,7 +5521,7 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -5546,7 +5546,7 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -5571,7 +5571,7 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -5596,7 +5596,7 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -5621,7 +5621,7 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -5646,7 +5646,7 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -5671,7 +5671,7 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -5696,7 +5696,7 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -5721,7 +5721,7 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -5746,7 +5746,7 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -5771,7 +5771,7 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -5796,7 +5796,7 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -5821,7 +5821,7 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -5846,7 +5846,7 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -5871,7 +5871,7 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -5896,7 +5896,7 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -5921,7 +5921,7 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -5946,7 +5946,7 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -5971,7 +5971,7 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -5996,7 +5996,7 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -6021,7 +6021,7 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -6046,7 +6046,7 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -6071,7 +6071,7 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -6096,7 +6096,7 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -6121,7 +6121,7 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -6146,7 +6146,7 @@
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -6171,7 +6171,7 @@
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -6196,7 +6196,7 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -6221,7 +6221,7 @@
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -6246,7 +6246,7 @@
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -6271,7 +6271,7 @@
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -6296,7 +6296,7 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -6321,7 +6321,7 @@
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -6346,7 +6346,7 @@
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -6371,7 +6371,7 @@
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -6396,7 +6396,7 @@
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -6421,7 +6421,7 @@
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -6446,7 +6446,7 @@
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -6471,7 +6471,7 @@
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -6496,7 +6496,7 @@
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -6521,7 +6521,7 @@
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
@@ -6546,7 +6546,7 @@
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
@@ -6571,7 +6571,7 @@
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
@@ -6596,7 +6596,7 @@
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
@@ -6621,7 +6621,7 @@
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
@@ -6646,7 +6646,7 @@
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
@@ -6671,7 +6671,7 @@
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
@@ -6696,7 +6696,7 @@
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
@@ -6721,7 +6721,7 @@
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
@@ -6746,7 +6746,7 @@
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
@@ -6771,7 +6771,7 @@
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
@@ -6796,7 +6796,7 @@
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
@@ -6821,7 +6821,7 @@
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
@@ -6846,7 +6846,7 @@
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
@@ -6871,7 +6871,7 @@
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
@@ -6896,7 +6896,7 @@
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
@@ -6921,7 +6921,7 @@
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
@@ -6946,7 +6946,7 @@
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
@@ -6971,7 +6971,7 @@
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
@@ -6996,7 +6996,7 @@
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
@@ -7021,7 +7021,7 @@
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
@@ -7046,7 +7046,7 @@
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
@@ -7071,7 +7071,7 @@
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
@@ -7096,7 +7096,7 @@
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
@@ -7121,7 +7121,7 @@
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
@@ -7146,7 +7146,7 @@
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
@@ -7171,7 +7171,7 @@
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
@@ -7196,7 +7196,7 @@
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
@@ -7221,7 +7221,7 @@
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
@@ -7246,7 +7246,7 @@
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
@@ -7271,7 +7271,7 @@
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
@@ -7296,7 +7296,7 @@
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
@@ -7321,7 +7321,7 @@
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
@@ -7346,7 +7346,7 @@
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
@@ -7371,7 +7371,7 @@
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
@@ -7396,7 +7396,7 @@
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
@@ -7421,7 +7421,7 @@
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
@@ -7446,7 +7446,7 @@
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
@@ -7471,7 +7471,7 @@
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
@@ -7496,7 +7496,7 @@
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
@@ -7521,7 +7521,7 @@
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
@@ -7546,7 +7546,7 @@
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
@@ -7571,7 +7571,7 @@
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
@@ -7596,7 +7596,7 @@
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
@@ -7621,7 +7621,7 @@
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
@@ -7646,7 +7646,7 @@
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
@@ -7671,7 +7671,7 @@
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
@@ -7696,7 +7696,7 @@
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
@@ -7721,7 +7721,7 @@
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
@@ -7746,7 +7746,7 @@
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
@@ -7771,7 +7771,7 @@
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
@@ -7796,7 +7796,7 @@
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
@@ -7821,7 +7821,7 @@
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
@@ -7846,7 +7846,7 @@
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
@@ -7871,7 +7871,7 @@
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
@@ -7896,7 +7896,7 @@
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
@@ -7921,7 +7921,7 @@
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
@@ -7946,7 +7946,7 @@
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
@@ -7971,7 +7971,7 @@
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
@@ -7996,7 +7996,7 @@
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
@@ -8021,7 +8021,7 @@
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
@@ -8046,7 +8046,7 @@
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
@@ -8071,7 +8071,7 @@
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
@@ -8096,7 +8096,7 @@
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
@@ -8121,7 +8121,7 @@
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
@@ -8146,7 +8146,7 @@
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
@@ -8171,7 +8171,7 @@
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
@@ -8196,7 +8196,7 @@
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
@@ -8221,7 +8221,7 @@
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
@@ -8246,7 +8246,7 @@
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
@@ -8271,7 +8271,7 @@
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
@@ -8296,7 +8296,7 @@
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
@@ -8321,7 +8321,7 @@
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
@@ -8346,7 +8346,7 @@
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
@@ -8371,7 +8371,7 @@
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
@@ -8396,7 +8396,7 @@
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
@@ -8421,7 +8421,7 @@
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
@@ -8446,7 +8446,7 @@
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
@@ -8471,7 +8471,7 @@
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
@@ -8496,7 +8496,7 @@
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
@@ -8521,7 +8521,7 @@
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
@@ -8546,7 +8546,7 @@
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
@@ -8571,7 +8571,7 @@
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
@@ -8596,7 +8596,7 @@
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
@@ -8621,7 +8621,7 @@
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
@@ -8646,7 +8646,7 @@
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B330" t="inlineStr">
@@ -8671,7 +8671,7 @@
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B331" t="inlineStr">
@@ -8696,7 +8696,7 @@
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B332" t="inlineStr">
@@ -8721,7 +8721,7 @@
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B333" t="inlineStr">
@@ -8746,7 +8746,7 @@
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B334" t="inlineStr">
@@ -8771,7 +8771,7 @@
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B335" t="inlineStr">
@@ -8796,7 +8796,7 @@
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B336" t="inlineStr">
@@ -8821,7 +8821,7 @@
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B337" t="inlineStr">
@@ -8846,7 +8846,7 @@
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B338" t="inlineStr">
@@ -8871,7 +8871,7 @@
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B339" t="inlineStr">
@@ -8896,7 +8896,7 @@
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B340" t="inlineStr">
@@ -8921,7 +8921,7 @@
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B341" t="inlineStr">
@@ -8946,7 +8946,7 @@
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B342" t="inlineStr">
@@ -8971,7 +8971,7 @@
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B343" t="inlineStr">
@@ -8996,7 +8996,7 @@
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B344" t="inlineStr">
@@ -9021,7 +9021,7 @@
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B345" t="inlineStr">
@@ -9046,7 +9046,7 @@
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B346" t="inlineStr">
@@ -9071,7 +9071,7 @@
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B347" t="inlineStr">
@@ -9096,7 +9096,7 @@
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B348" t="inlineStr">
@@ -9121,7 +9121,7 @@
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B349" t="inlineStr">
@@ -9146,7 +9146,7 @@
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B350" t="inlineStr">
@@ -9171,7 +9171,7 @@
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B351" t="inlineStr">
@@ -9196,7 +9196,7 @@
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B352" t="inlineStr">
@@ -9221,7 +9221,7 @@
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B353" t="inlineStr">
@@ -9246,7 +9246,7 @@
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B354" t="inlineStr">
@@ -9271,7 +9271,7 @@
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B355" t="inlineStr">
@@ -9296,7 +9296,7 @@
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B356" t="inlineStr">
@@ -9321,7 +9321,7 @@
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B357" t="inlineStr">
@@ -9346,7 +9346,7 @@
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B358" t="inlineStr">
@@ -9371,7 +9371,7 @@
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B359" t="inlineStr">
@@ -9396,7 +9396,7 @@
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B360" t="inlineStr">
@@ -9421,7 +9421,7 @@
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B361" t="inlineStr">
@@ -9446,7 +9446,7 @@
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B362" t="inlineStr">
@@ -9471,7 +9471,7 @@
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B363" t="inlineStr">
@@ -9496,7 +9496,7 @@
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B364" t="inlineStr">
@@ -9521,7 +9521,7 @@
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B365" t="inlineStr">
@@ -9546,7 +9546,7 @@
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B366" t="inlineStr">
@@ -9571,7 +9571,7 @@
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B367" t="inlineStr">
@@ -9596,7 +9596,7 @@
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B368" t="inlineStr">
@@ -9621,7 +9621,7 @@
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B369" t="inlineStr">
@@ -9646,7 +9646,7 @@
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B370" t="inlineStr">
@@ -9671,7 +9671,7 @@
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B371" t="inlineStr">
@@ -9696,7 +9696,7 @@
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B372" t="inlineStr">
@@ -9721,7 +9721,7 @@
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B373" t="inlineStr">
@@ -9746,7 +9746,7 @@
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B374" t="inlineStr">
@@ -9771,7 +9771,7 @@
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B375" t="inlineStr">
@@ -9796,7 +9796,7 @@
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B376" t="inlineStr">
@@ -9821,7 +9821,7 @@
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B377" t="inlineStr">
@@ -9846,7 +9846,7 @@
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B378" t="inlineStr">
@@ -9871,7 +9871,7 @@
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B379" t="inlineStr">
@@ -9896,7 +9896,7 @@
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B380" t="inlineStr">
@@ -9921,7 +9921,7 @@
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B381" t="inlineStr">
@@ -9946,7 +9946,7 @@
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B382" t="inlineStr">
@@ -9971,7 +9971,7 @@
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B383" t="inlineStr">
@@ -9996,7 +9996,7 @@
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B384" t="inlineStr">
@@ -10021,7 +10021,7 @@
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B385" t="inlineStr">
@@ -10046,7 +10046,7 @@
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B386" t="inlineStr">
@@ -10071,7 +10071,7 @@
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B387" t="inlineStr">
@@ -10096,7 +10096,7 @@
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B388" t="inlineStr">
@@ -10121,7 +10121,7 @@
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B389" t="inlineStr">
@@ -10146,7 +10146,7 @@
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B390" t="inlineStr">
@@ -10171,7 +10171,7 @@
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B391" t="inlineStr">
@@ -10196,7 +10196,7 @@
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B392" t="inlineStr">
@@ -10221,7 +10221,7 @@
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B393" t="inlineStr">
@@ -10246,7 +10246,7 @@
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B394" t="inlineStr">
@@ -10271,7 +10271,7 @@
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B395" t="inlineStr">
@@ -10296,7 +10296,7 @@
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B396" t="inlineStr">
@@ -10321,7 +10321,7 @@
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B397" t="inlineStr">
@@ -10346,7 +10346,7 @@
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B398" t="inlineStr">
@@ -10371,7 +10371,7 @@
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B399" t="inlineStr">
@@ -10396,7 +10396,7 @@
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B400" t="inlineStr">
@@ -10421,7 +10421,7 @@
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B401" t="inlineStr">
@@ -10446,7 +10446,7 @@
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B402" t="inlineStr">
@@ -10471,7 +10471,7 @@
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B403" t="inlineStr">
@@ -10496,7 +10496,7 @@
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B404" t="inlineStr">
@@ -10521,7 +10521,7 @@
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B405" t="inlineStr">
@@ -10546,7 +10546,7 @@
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B406" t="inlineStr">
@@ -10571,7 +10571,7 @@
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B407" t="inlineStr">
@@ -10596,7 +10596,7 @@
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B408" t="inlineStr">
@@ -10621,7 +10621,7 @@
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B409" t="inlineStr">
@@ -10646,7 +10646,7 @@
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B410" t="inlineStr">
@@ -10671,7 +10671,7 @@
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B411" t="inlineStr">
@@ -10696,7 +10696,7 @@
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B412" t="inlineStr">
@@ -10721,7 +10721,7 @@
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B413" t="inlineStr">
@@ -10746,7 +10746,7 @@
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B414" t="inlineStr">
@@ -10771,7 +10771,7 @@
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B415" t="inlineStr">
@@ -10796,7 +10796,7 @@
     <row r="416">
       <c r="A416" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B416" t="inlineStr">
@@ -10821,7 +10821,7 @@
     <row r="417">
       <c r="A417" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B417" t="inlineStr">
@@ -10846,7 +10846,7 @@
     <row r="418">
       <c r="A418" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B418" t="inlineStr">
@@ -10871,7 +10871,7 @@
     <row r="419">
       <c r="A419" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B419" t="inlineStr">
@@ -10896,7 +10896,7 @@
     <row r="420">
       <c r="A420" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B420" t="inlineStr">
@@ -10921,7 +10921,7 @@
     <row r="421">
       <c r="A421" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B421" t="inlineStr">
@@ -10946,7 +10946,7 @@
     <row r="422">
       <c r="A422" t="inlineStr">
         <is>
-          <t>26020711</t>
+          <t>PO 2602-0711</t>
         </is>
       </c>
       <c r="B422" t="inlineStr">
@@ -10971,7 +10971,7 @@
     <row r="423">
       <c r="A423" t="inlineStr">
         <is>
-          <t>26030989</t>
+          <t>PO 2603-0989</t>
         </is>
       </c>
       <c r="B423" t="inlineStr">
@@ -10996,7 +10996,7 @@
     <row r="424">
       <c r="A424" t="inlineStr">
         <is>
-          <t>26030989</t>
+          <t>PO 2603-0989</t>
         </is>
       </c>
       <c r="B424" t="inlineStr">
@@ -11021,7 +11021,7 @@
     <row r="425">
       <c r="A425" t="inlineStr">
         <is>
-          <t>26030989</t>
+          <t>PO 2603-0989</t>
         </is>
       </c>
       <c r="B425" t="inlineStr">
@@ -11046,7 +11046,7 @@
     <row r="426">
       <c r="A426" t="inlineStr">
         <is>
-          <t>26030989</t>
+          <t>PO 2603-0989</t>
         </is>
       </c>
       <c r="B426" t="inlineStr">
@@ -11071,7 +11071,7 @@
     <row r="427">
       <c r="A427" t="inlineStr">
         <is>
-          <t>26030989</t>
+          <t>PO 2603-0989</t>
         </is>
       </c>
       <c r="B427" t="inlineStr">
@@ -11096,7 +11096,7 @@
     <row r="428">
       <c r="A428" t="inlineStr">
         <is>
-          <t>26030989</t>
+          <t>PO 2603-0989</t>
         </is>
       </c>
       <c r="B428" t="inlineStr">
@@ -11121,7 +11121,7 @@
     <row r="429">
       <c r="A429" t="inlineStr">
         <is>
-          <t>26030989</t>
+          <t>PO 2603-0989</t>
         </is>
       </c>
       <c r="B429" t="inlineStr">
@@ -11146,7 +11146,7 @@
     <row r="430">
       <c r="A430" t="inlineStr">
         <is>
-          <t>26030989</t>
+          <t>PO 2603-0989</t>
         </is>
       </c>
       <c r="B430" t="inlineStr">
@@ -11171,7 +11171,7 @@
     <row r="431">
       <c r="A431" t="inlineStr">
         <is>
-          <t>26030989</t>
+          <t>PO 2603-0989</t>
         </is>
       </c>
       <c r="B431" t="inlineStr">
@@ -11196,7 +11196,7 @@
     <row r="432">
       <c r="A432" t="inlineStr">
         <is>
-          <t>26030989</t>
+          <t>PO 2603-0989</t>
         </is>
       </c>
       <c r="B432" t="inlineStr">
@@ -11221,7 +11221,7 @@
     <row r="433">
       <c r="A433" t="inlineStr">
         <is>
-          <t>26030989</t>
+          <t>PO 2603-0989</t>
         </is>
       </c>
       <c r="B433" t="inlineStr">
@@ -11246,7 +11246,7 @@
     <row r="434">
       <c r="A434" t="inlineStr">
         <is>
-          <t>26030989</t>
+          <t>PO 2603-0989</t>
         </is>
       </c>
       <c r="B434" t="inlineStr">
@@ -11271,7 +11271,7 @@
     <row r="435">
       <c r="A435" t="inlineStr">
         <is>
-          <t>26030989</t>
+          <t>PO 2603-0989</t>
         </is>
       </c>
       <c r="B435" t="inlineStr">
@@ -11296,7 +11296,7 @@
     <row r="436">
       <c r="A436" t="inlineStr">
         <is>
-          <t>26030989</t>
+          <t>PO 2603-0989</t>
         </is>
       </c>
       <c r="B436" t="inlineStr">
@@ -11321,7 +11321,7 @@
     <row r="437">
       <c r="A437" t="inlineStr">
         <is>
-          <t>26030989</t>
+          <t>PO 2603-0989</t>
         </is>
       </c>
       <c r="B437" t="inlineStr">
@@ -11346,7 +11346,7 @@
     <row r="438">
       <c r="A438" t="inlineStr">
         <is>
-          <t>26030989</t>
+          <t>PO 2603-0989</t>
         </is>
       </c>
       <c r="B438" t="inlineStr">
@@ -11371,7 +11371,7 @@
     <row r="439">
       <c r="A439" t="inlineStr">
         <is>
-          <t>26030989</t>
+          <t>PO 2603-0989</t>
         </is>
       </c>
       <c r="B439" t="inlineStr">
